--- a/scripts/adhoc/outputs/alt_kanaele_long_sample.xlsx
+++ b/scripts/adhoc/outputs/alt_kanaele_long_sample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bened\PycharmProjects\youtube_data\scripts\adhoc\outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B83B198-2BA2-433B-83B8-1043515C01AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A9FFD9F-6D97-48AD-974C-94FD069E6B1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3797,7 +3797,7 @@
         <v>261</v>
       </c>
       <c r="E122">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.45">
